--- a/artfynd/A 37224-2026 artfynd.xlsx
+++ b/artfynd/A 37224-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136757869</v>
       </c>
       <c r="B2" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136757877</v>
       </c>
       <c r="B3" t="n">
-        <v>58870</v>
+        <v>58872</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37224-2026 artfynd.xlsx
+++ b/artfynd/A 37224-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136757869</v>
       </c>
       <c r="B2" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136757877</v>
       </c>
       <c r="B3" t="n">
-        <v>58872</v>
+        <v>58885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37224-2026 artfynd.xlsx
+++ b/artfynd/A 37224-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136757869</v>
       </c>
       <c r="B2" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>136757877</v>
       </c>
       <c r="B3" t="n">
-        <v>58885</v>
+        <v>58887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37224-2026 artfynd.xlsx
+++ b/artfynd/A 37224-2026 artfynd.xlsx
@@ -714,11 +714,7 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -830,11 +826,7 @@
         </is>
       </c>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>årsunge</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>

--- a/artfynd/A 37224-2026 artfynd.xlsx
+++ b/artfynd/A 37224-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136757869</v>
       </c>
       <c r="B2" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136757877</v>
       </c>
       <c r="B3" t="n">
-        <v>58887</v>
+        <v>58897</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
